--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_WB_Assumptions.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_WB_Assumptions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\MyModels\VerveStacks_POL_grids_kan50\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131832E2-B034-455D-A9FB-755C55442812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415C6144-D8DA-4D2D-8CD6-6E4174694F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="assumptions" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -126,6 +126,18 @@
   </si>
   <si>
     <t>p_co2_*</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>UCE_max nuclear capacity</t>
+  </si>
+  <si>
+    <t>~TFM_UPD</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
   </si>
 </sst>
 </file>
@@ -546,32 +558,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
-  <dimension ref="A2:J33"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:O33"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.19921875" customWidth="1"/>
+    <col min="3" max="3" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.53125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.46484375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -596,8 +614,17 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -613,8 +640,17 @@
       <c r="H8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
@@ -633,15 +669,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B10" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>9</v>
       </c>
@@ -652,7 +688,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>12</v>
       </c>
@@ -663,14 +699,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -681,7 +717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
@@ -692,17 +728,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>22</v>
       </c>
@@ -716,7 +752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -727,12 +763,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B26" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
         <v>2</v>
       </c>
@@ -764,7 +800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>27</v>
       </c>
@@ -787,12 +823,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>22</v>
       </c>
@@ -806,7 +842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>24</v>
       </c>
@@ -818,7 +854,7 @@
         <v>solar</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>24</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_WB_Assumptions.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_WB_Assumptions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415C6144-D8DA-4D2D-8CD6-6E4174694F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21FAF91-02ED-4455-AE2C-BE9823F49776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,7 +585,7 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -614,13 +614,13 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
